--- a/backtest_runs/20260410_193731/by_symbol/SAIF/SAIF.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SAIF/SAIF.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-6492.980000000005</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100461.04</v>
@@ -679,7 +679,7 @@
         <v>-10258.13999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>90202.90000000001</v>
@@ -863,7 +863,7 @@
         <v>-1844.160000000002</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>92777.04000000001</v>
@@ -909,7 +909,7 @@
         <v>-7107.700000000005</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>85669.34</v>
@@ -1093,7 +1093,7 @@
         <v>-4687.240000000009</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>88205.06</v>
@@ -1185,7 +1185,7 @@
         <v>-3380.959999999996</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>88935.04000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-3573.059999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>85361.98000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-4110.940000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>81251.04000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-268.9400000000011</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>90318.16</v>
@@ -1553,7 +1553,7 @@
         <v>-307.3599999999934</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>90010.8</v>
@@ -1645,7 +1645,7 @@
         <v>-4495.140000000007</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>91355.5</v>
